--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F9F7281-DB77-43F5-9097-B5CD9F603AB7}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9680B38-DC4F-4E26-B5F3-694EC9A52BB1}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -255,10 +255,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,7 +607,7 @@
       </c>
       <c r="B4" s="13">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C4" s="13">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -619,7 +615,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.3066923076923078</v>
+        <v>1.2133571428571428</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -628,15 +624,15 @@
       </c>
       <c r="B5" s="13">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C5" s="13">
         <f>SUM(Rounds!C7:BB7)</f>
-        <v>278.43</v>
+        <v>319.43</v>
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.0708846153846154</v>
+        <v>1.1408214285714287</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,7 +641,7 @@
       </c>
       <c r="B6" s="13">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C6" s="13">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -653,7 +649,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>0.85134615384615386</v>
+        <v>0.79053571428571423</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -662,7 +658,7 @@
       </c>
       <c r="B7" s="13">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C7" s="13">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -670,7 +666,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.1841923076923075</v>
+        <v>1.0996071428571428</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -679,15 +675,15 @@
       </c>
       <c r="B8" s="13">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C8" s="13">
         <f>SUM(Rounds!C10:BB10)</f>
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.63846153846153841</v>
+        <v>0.71785714285714286</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -696,7 +692,7 @@
       </c>
       <c r="B9" s="13">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C9" s="13">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -704,7 +700,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.96826923076923077</v>
+        <v>0.89910714285714288</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -713,15 +709,15 @@
       </c>
       <c r="B10" s="13">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C10" s="13">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>278.18</v>
+        <v>292.68</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.069923076923077</v>
+        <v>1.0452857142857144</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -730,7 +726,7 @@
       </c>
       <c r="B11" s="13">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C11" s="13">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -738,7 +734,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.84573076923076917</v>
+        <v>0.7853214285714285</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -747,7 +743,7 @@
       </c>
       <c r="B12" s="13">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -755,7 +751,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.50192307692307692</v>
+        <v>0.46607142857142858</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -764,7 +760,7 @@
       </c>
       <c r="B13" s="13">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C13" s="13">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -772,7 +768,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.81130769230769229</v>
+        <v>0.75335714285714284</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -787,15 +783,15 @@
       </c>
       <c r="B15" s="15">
         <f>SUM(B4:B13)</f>
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="C15" s="14">
         <f>SUM(C4:C13)</f>
-        <v>2404.67</v>
+        <v>2495.17</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.92487307692307696</v>
+        <v>0.89113214285714293</v>
       </c>
     </row>
   </sheetData>
@@ -828,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1148,7 +1144,9 @@
         <v>67.709999999999994</v>
       </c>
       <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
+      <c r="P7" s="17">
+        <v>41</v>
+      </c>
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
@@ -1351,7 +1349,9 @@
       <c r="O10" s="17">
         <v>20</v>
       </c>
-      <c r="P10" s="17"/>
+      <c r="P10" s="17">
+        <v>35</v>
+      </c>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
@@ -1500,7 +1500,9 @@
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
+      <c r="P12" s="17">
+        <v>14.5</v>
+      </c>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
@@ -1805,7 +1807,7 @@
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="12">SUM(P6:P15)</f>
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="Q16" s="18">
         <f t="shared" ref="Q16" si="13">SUM(Q6:Q15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9680B38-DC4F-4E26-B5F3-694EC9A52BB1}"/>
+  <xr:revisionPtr revIDLastSave="323" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{407F8550-187A-4887-B692-174281A0AF5A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
+    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Phil</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Puntoff - Summary</t>
+  </si>
+  <si>
+    <t>Sportsbet Balance</t>
   </si>
 </sst>
 </file>
@@ -207,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -227,10 +230,6 @@
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -239,6 +238,18 @@
     </xf>
     <xf numFmtId="7" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="7" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -597,7 +608,7 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -605,11 +616,11 @@
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <f>+Rounds!B6*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="11">
         <f>SUM(Rounds!C6:BB6)</f>
         <v>339.74</v>
       </c>
@@ -622,11 +633,11 @@
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <f>+Rounds!B7*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="11">
         <f>SUM(Rounds!C7:BB7)</f>
         <v>319.43</v>
       </c>
@@ -639,11 +650,11 @@
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <f>+Rounds!B8*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <f>SUM(Rounds!C8:BB8)</f>
         <v>221.35</v>
       </c>
@@ -656,11 +667,11 @@
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <f>+Rounds!B9*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <f>SUM(Rounds!C9:BB9)</f>
         <v>307.89</v>
       </c>
@@ -673,11 +684,11 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <f>+Rounds!B10*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <f>SUM(Rounds!C10:BB10)</f>
         <v>201</v>
       </c>
@@ -690,11 +701,11 @@
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <f>+Rounds!B11*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <f>SUM(Rounds!C11:BB11)</f>
         <v>251.75</v>
       </c>
@@ -707,11 +718,11 @@
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <f>+Rounds!B12*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <f>SUM(Rounds!C12:BB12)</f>
         <v>292.68</v>
       </c>
@@ -724,11 +735,11 @@
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <f>+Rounds!B13*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="11">
         <f>SUM(Rounds!C13:BB13)</f>
         <v>219.89</v>
       </c>
@@ -741,11 +752,11 @@
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <f>+Rounds!B14*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="11">
         <f>SUM(Rounds!C14:BB14)</f>
         <v>130.5</v>
       </c>
@@ -758,11 +769,11 @@
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <f>+Rounds!B15*Rounds!$B$3</f>
         <v>280</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="11">
         <f>SUM(Rounds!C15:BB15)</f>
         <v>210.94</v>
       </c>
@@ -773,19 +784,19 @@
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="13">
         <f>SUM(B4:B13)</f>
         <v>2800</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="12">
         <f>SUM(C4:C13)</f>
         <v>2495.17</v>
       </c>
@@ -814,16 +825,24 @@
     <col min="3" max="54" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:54" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+    <row r="2" spans="1:54" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="18">
+        <v>690.33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="19">
         <v>14</v>
       </c>
     </row>
@@ -1049,915 +1068,915 @@
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>20</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="15">
         <v>43.74</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17">
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15">
         <v>88</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="15">
         <v>64</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="15">
         <v>76</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17">
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15">
         <v>68</v>
       </c>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="17"/>
-      <c r="AH6" s="17"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="17"/>
-      <c r="AK6" s="17"/>
-      <c r="AL6" s="17"/>
-      <c r="AM6" s="17"/>
-      <c r="AN6" s="17"/>
-      <c r="AO6" s="17"/>
-      <c r="AP6" s="17"/>
-      <c r="AQ6" s="17"/>
-      <c r="AR6" s="17"/>
-      <c r="AS6" s="17"/>
-      <c r="AT6" s="17"/>
-      <c r="AU6" s="17"/>
-      <c r="AV6" s="17"/>
-      <c r="AW6" s="17"/>
-      <c r="AX6" s="17"/>
-      <c r="AY6" s="17"/>
-      <c r="AZ6" s="17"/>
-      <c r="BA6" s="17"/>
-      <c r="BB6" s="17"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="15"/>
+      <c r="AK6" s="15"/>
+      <c r="AL6" s="15"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
+      <c r="AO6" s="15"/>
+      <c r="AP6" s="15"/>
+      <c r="AQ6" s="15"/>
+      <c r="AR6" s="15"/>
+      <c r="AS6" s="15"/>
+      <c r="AT6" s="15"/>
+      <c r="AU6" s="15"/>
+      <c r="AV6" s="15"/>
+      <c r="AW6" s="15"/>
+      <c r="AX6" s="15"/>
+      <c r="AY6" s="15"/>
+      <c r="AZ6" s="15"/>
+      <c r="BA6" s="15"/>
+      <c r="BB6" s="15"/>
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="15">
         <f>+B6</f>
         <v>20</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17">
+      <c r="C7" s="15"/>
+      <c r="D7" s="15">
         <v>40</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17">
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15">
         <v>150</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17">
+      <c r="I7" s="15"/>
+      <c r="J7" s="15">
         <v>20.72</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17">
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15">
         <v>67.709999999999994</v>
       </c>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17">
+      <c r="O7" s="15"/>
+      <c r="P7" s="15">
         <v>41</v>
       </c>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="17"/>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="17"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="17"/>
-      <c r="AF7" s="17"/>
-      <c r="AG7" s="17"/>
-      <c r="AH7" s="17"/>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="17"/>
-      <c r="AK7" s="17"/>
-      <c r="AL7" s="17"/>
-      <c r="AM7" s="17"/>
-      <c r="AN7" s="17"/>
-      <c r="AO7" s="17"/>
-      <c r="AP7" s="17"/>
-      <c r="AQ7" s="17"/>
-      <c r="AR7" s="17"/>
-      <c r="AS7" s="17"/>
-      <c r="AT7" s="17"/>
-      <c r="AU7" s="17"/>
-      <c r="AV7" s="17"/>
-      <c r="AW7" s="17"/>
-      <c r="AX7" s="17"/>
-      <c r="AY7" s="17"/>
-      <c r="AZ7" s="17"/>
-      <c r="BA7" s="17"/>
-      <c r="BB7" s="17"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="15"/>
+      <c r="AC7" s="15"/>
+      <c r="AD7" s="15"/>
+      <c r="AE7" s="15"/>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="15"/>
+      <c r="AH7" s="15"/>
+      <c r="AI7" s="15"/>
+      <c r="AJ7" s="15"/>
+      <c r="AK7" s="15"/>
+      <c r="AL7" s="15"/>
+      <c r="AM7" s="15"/>
+      <c r="AN7" s="15"/>
+      <c r="AO7" s="15"/>
+      <c r="AP7" s="15"/>
+      <c r="AQ7" s="15"/>
+      <c r="AR7" s="15"/>
+      <c r="AS7" s="15"/>
+      <c r="AT7" s="15"/>
+      <c r="AU7" s="15"/>
+      <c r="AV7" s="15"/>
+      <c r="AW7" s="15"/>
+      <c r="AX7" s="15"/>
+      <c r="AY7" s="15"/>
+      <c r="AZ7" s="15"/>
+      <c r="BA7" s="15"/>
+      <c r="BB7" s="15"/>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="15">
         <f t="shared" ref="B8:B15" si="3">+B7</f>
         <v>20</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="15">
         <v>44.7</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17">
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15">
         <v>70</v>
       </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17">
+      <c r="G8" s="15"/>
+      <c r="H8" s="15">
         <v>65.67</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="15">
         <v>40.98</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="17"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="17"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="17"/>
-      <c r="AN8" s="17"/>
-      <c r="AO8" s="17"/>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="17"/>
-      <c r="AR8" s="17"/>
-      <c r="AS8" s="17"/>
-      <c r="AT8" s="17"/>
-      <c r="AU8" s="17"/>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="17"/>
-      <c r="AX8" s="17"/>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="17"/>
-      <c r="BA8" s="17"/>
-      <c r="BB8" s="17"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="15"/>
+      <c r="AC8" s="15"/>
+      <c r="AD8" s="15"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="15"/>
+      <c r="AH8" s="15"/>
+      <c r="AI8" s="15"/>
+      <c r="AJ8" s="15"/>
+      <c r="AK8" s="15"/>
+      <c r="AL8" s="15"/>
+      <c r="AM8" s="15"/>
+      <c r="AN8" s="15"/>
+      <c r="AO8" s="15"/>
+      <c r="AP8" s="15"/>
+      <c r="AQ8" s="15"/>
+      <c r="AR8" s="15"/>
+      <c r="AS8" s="15"/>
+      <c r="AT8" s="15"/>
+      <c r="AU8" s="15"/>
+      <c r="AV8" s="15"/>
+      <c r="AW8" s="15"/>
+      <c r="AX8" s="15"/>
+      <c r="AY8" s="15"/>
+      <c r="AZ8" s="15"/>
+      <c r="BA8" s="15"/>
+      <c r="BB8" s="15"/>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="15">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="15">
         <v>82.35</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17">
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15">
         <v>75</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15">
         <v>150.54</v>
       </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="17"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="17"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="17"/>
-      <c r="AM9" s="17"/>
-      <c r="AN9" s="17"/>
-      <c r="AO9" s="17"/>
-      <c r="AP9" s="17"/>
-      <c r="AQ9" s="17"/>
-      <c r="AR9" s="17"/>
-      <c r="AS9" s="17"/>
-      <c r="AT9" s="17"/>
-      <c r="AU9" s="17"/>
-      <c r="AV9" s="17"/>
-      <c r="AW9" s="17"/>
-      <c r="AX9" s="17"/>
-      <c r="AY9" s="17"/>
-      <c r="AZ9" s="17"/>
-      <c r="BA9" s="17"/>
-      <c r="BB9" s="17"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="15"/>
+      <c r="AC9" s="15"/>
+      <c r="AD9" s="15"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="15"/>
+      <c r="AH9" s="15"/>
+      <c r="AI9" s="15"/>
+      <c r="AJ9" s="15"/>
+      <c r="AK9" s="15"/>
+      <c r="AL9" s="15"/>
+      <c r="AM9" s="15"/>
+      <c r="AN9" s="15"/>
+      <c r="AO9" s="15"/>
+      <c r="AP9" s="15"/>
+      <c r="AQ9" s="15"/>
+      <c r="AR9" s="15"/>
+      <c r="AS9" s="15"/>
+      <c r="AT9" s="15"/>
+      <c r="AU9" s="15"/>
+      <c r="AV9" s="15"/>
+      <c r="AW9" s="15"/>
+      <c r="AX9" s="15"/>
+      <c r="AY9" s="15"/>
+      <c r="AZ9" s="15"/>
+      <c r="BA9" s="15"/>
+      <c r="BB9" s="15"/>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="15">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="15">
         <v>80</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17">
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15">
         <v>66</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17">
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15">
         <v>20</v>
       </c>
-      <c r="P10" s="17">
+      <c r="P10" s="15">
         <v>35</v>
       </c>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
-      <c r="AK10" s="17"/>
-      <c r="AL10" s="17"/>
-      <c r="AM10" s="17"/>
-      <c r="AN10" s="17"/>
-      <c r="AO10" s="17"/>
-      <c r="AP10" s="17"/>
-      <c r="AQ10" s="17"/>
-      <c r="AR10" s="17"/>
-      <c r="AS10" s="17"/>
-      <c r="AT10" s="17"/>
-      <c r="AU10" s="17"/>
-      <c r="AV10" s="17"/>
-      <c r="AW10" s="17"/>
-      <c r="AX10" s="17"/>
-      <c r="AY10" s="17"/>
-      <c r="AZ10" s="17"/>
-      <c r="BA10" s="17"/>
-      <c r="BB10" s="17"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="15"/>
+      <c r="AN10" s="15"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+      <c r="AS10" s="15"/>
+      <c r="AT10" s="15"/>
+      <c r="AU10" s="15"/>
+      <c r="AV10" s="15"/>
+      <c r="AW10" s="15"/>
+      <c r="AX10" s="15"/>
+      <c r="AY10" s="15"/>
+      <c r="AZ10" s="15"/>
+      <c r="BA10" s="15"/>
+      <c r="BB10" s="15"/>
     </row>
     <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="15">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="15">
         <v>34</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17">
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15">
         <v>37.5</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="15">
         <v>67.5</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17">
+      <c r="H11" s="15"/>
+      <c r="I11" s="15">
         <v>59</v>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17">
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15">
         <v>36.25</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="15">
         <v>17.5</v>
       </c>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="17"/>
-      <c r="AO11" s="17"/>
-      <c r="AP11" s="17"/>
-      <c r="AQ11" s="17"/>
-      <c r="AR11" s="17"/>
-      <c r="AS11" s="17"/>
-      <c r="AT11" s="17"/>
-      <c r="AU11" s="17"/>
-      <c r="AV11" s="17"/>
-      <c r="AW11" s="17"/>
-      <c r="AX11" s="17"/>
-      <c r="AY11" s="17"/>
-      <c r="AZ11" s="17"/>
-      <c r="BA11" s="17"/>
-      <c r="BB11" s="17"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15"/>
+      <c r="AB11" s="15"/>
+      <c r="AC11" s="15"/>
+      <c r="AD11" s="15"/>
+      <c r="AE11" s="15"/>
+      <c r="AF11" s="15"/>
+      <c r="AG11" s="15"/>
+      <c r="AH11" s="15"/>
+      <c r="AI11" s="15"/>
+      <c r="AJ11" s="15"/>
+      <c r="AK11" s="15"/>
+      <c r="AL11" s="15"/>
+      <c r="AM11" s="15"/>
+      <c r="AN11" s="15"/>
+      <c r="AO11" s="15"/>
+      <c r="AP11" s="15"/>
+      <c r="AQ11" s="15"/>
+      <c r="AR11" s="15"/>
+      <c r="AS11" s="15"/>
+      <c r="AT11" s="15"/>
+      <c r="AU11" s="15"/>
+      <c r="AV11" s="15"/>
+      <c r="AW11" s="15"/>
+      <c r="AX11" s="15"/>
+      <c r="AY11" s="15"/>
+      <c r="AZ11" s="15"/>
+      <c r="BA11" s="15"/>
+      <c r="BB11" s="15"/>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="15">
         <v>44.19</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17">
+      <c r="D12" s="15"/>
+      <c r="E12" s="15">
         <v>25</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17">
+      <c r="F12" s="15"/>
+      <c r="G12" s="15">
         <v>20</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17">
+      <c r="H12" s="15"/>
+      <c r="I12" s="15">
         <f>18.13+35</f>
         <v>53.129999999999995</v>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17">
+      <c r="J12" s="15"/>
+      <c r="K12" s="15">
         <v>50</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="15">
         <v>49</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="15">
         <v>36.86</v>
       </c>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17">
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15">
         <v>14.5</v>
       </c>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="17"/>
-      <c r="AP12" s="17"/>
-      <c r="AQ12" s="17"/>
-      <c r="AR12" s="17"/>
-      <c r="AS12" s="17"/>
-      <c r="AT12" s="17"/>
-      <c r="AU12" s="17"/>
-      <c r="AV12" s="17"/>
-      <c r="AW12" s="17"/>
-      <c r="AX12" s="17"/>
-      <c r="AY12" s="17"/>
-      <c r="AZ12" s="17"/>
-      <c r="BA12" s="17"/>
-      <c r="BB12" s="17"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="15"/>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="15"/>
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="15"/>
+      <c r="AJ12" s="15"/>
+      <c r="AK12" s="15"/>
+      <c r="AL12" s="15"/>
+      <c r="AM12" s="15"/>
+      <c r="AN12" s="15"/>
+      <c r="AO12" s="15"/>
+      <c r="AP12" s="15"/>
+      <c r="AQ12" s="15"/>
+      <c r="AR12" s="15"/>
+      <c r="AS12" s="15"/>
+      <c r="AT12" s="15"/>
+      <c r="AU12" s="15"/>
+      <c r="AV12" s="15"/>
+      <c r="AW12" s="15"/>
+      <c r="AX12" s="15"/>
+      <c r="AY12" s="15"/>
+      <c r="AZ12" s="15"/>
+      <c r="BA12" s="15"/>
+      <c r="BB12" s="15"/>
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15">
         <v>34</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <v>50</v>
       </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17">
+      <c r="I13" s="15"/>
+      <c r="J13" s="15">
         <v>15.89</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17">
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15">
         <v>120</v>
       </c>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
-      <c r="AG13" s="17"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="17"/>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17"/>
-      <c r="AP13" s="17"/>
-      <c r="AQ13" s="17"/>
-      <c r="AR13" s="17"/>
-      <c r="AS13" s="17"/>
-      <c r="AT13" s="17"/>
-      <c r="AU13" s="17"/>
-      <c r="AV13" s="17"/>
-      <c r="AW13" s="17"/>
-      <c r="AX13" s="17"/>
-      <c r="AY13" s="17"/>
-      <c r="AZ13" s="17"/>
-      <c r="BA13" s="17"/>
-      <c r="BB13" s="17"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="15"/>
+      <c r="AC13" s="15"/>
+      <c r="AD13" s="15"/>
+      <c r="AE13" s="15"/>
+      <c r="AF13" s="15"/>
+      <c r="AG13" s="15"/>
+      <c r="AH13" s="15"/>
+      <c r="AI13" s="15"/>
+      <c r="AJ13" s="15"/>
+      <c r="AK13" s="15"/>
+      <c r="AL13" s="15"/>
+      <c r="AM13" s="15"/>
+      <c r="AN13" s="15"/>
+      <c r="AO13" s="15"/>
+      <c r="AP13" s="15"/>
+      <c r="AQ13" s="15"/>
+      <c r="AR13" s="15"/>
+      <c r="AS13" s="15"/>
+      <c r="AT13" s="15"/>
+      <c r="AU13" s="15"/>
+      <c r="AV13" s="15"/>
+      <c r="AW13" s="15"/>
+      <c r="AX13" s="15"/>
+      <c r="AY13" s="15"/>
+      <c r="AZ13" s="15"/>
+      <c r="BA13" s="15"/>
+      <c r="BB13" s="15"/>
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="15">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15">
         <v>70</v>
       </c>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17">
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15">
         <v>37</v>
       </c>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17">
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15">
         <v>23.5</v>
       </c>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="17"/>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="17"/>
-      <c r="AF14" s="17"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="17"/>
-      <c r="AI14" s="17"/>
-      <c r="AJ14" s="17"/>
-      <c r="AK14" s="17"/>
-      <c r="AL14" s="17"/>
-      <c r="AM14" s="17"/>
-      <c r="AN14" s="17"/>
-      <c r="AO14" s="17"/>
-      <c r="AP14" s="17"/>
-      <c r="AQ14" s="17"/>
-      <c r="AR14" s="17"/>
-      <c r="AS14" s="17"/>
-      <c r="AT14" s="17"/>
-      <c r="AU14" s="17"/>
-      <c r="AV14" s="17"/>
-      <c r="AW14" s="17"/>
-      <c r="AX14" s="17"/>
-      <c r="AY14" s="17"/>
-      <c r="AZ14" s="17"/>
-      <c r="BA14" s="17"/>
-      <c r="BB14" s="17"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="15"/>
+      <c r="AE14" s="15"/>
+      <c r="AF14" s="15"/>
+      <c r="AG14" s="15"/>
+      <c r="AH14" s="15"/>
+      <c r="AI14" s="15"/>
+      <c r="AJ14" s="15"/>
+      <c r="AK14" s="15"/>
+      <c r="AL14" s="15"/>
+      <c r="AM14" s="15"/>
+      <c r="AN14" s="15"/>
+      <c r="AO14" s="15"/>
+      <c r="AP14" s="15"/>
+      <c r="AQ14" s="15"/>
+      <c r="AR14" s="15"/>
+      <c r="AS14" s="15"/>
+      <c r="AT14" s="15"/>
+      <c r="AU14" s="15"/>
+      <c r="AV14" s="15"/>
+      <c r="AW14" s="15"/>
+      <c r="AX14" s="15"/>
+      <c r="AY14" s="15"/>
+      <c r="AZ14" s="15"/>
+      <c r="BA14" s="15"/>
+      <c r="BB14" s="15"/>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="15">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15">
         <v>12.44</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="15">
         <v>18.5</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17">
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15">
         <v>180</v>
       </c>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="17"/>
-      <c r="AE15" s="17"/>
-      <c r="AF15" s="17"/>
-      <c r="AG15" s="17"/>
-      <c r="AH15" s="17"/>
-      <c r="AI15" s="17"/>
-      <c r="AJ15" s="17"/>
-      <c r="AK15" s="17"/>
-      <c r="AL15" s="17"/>
-      <c r="AM15" s="17"/>
-      <c r="AN15" s="17"/>
-      <c r="AO15" s="17"/>
-      <c r="AP15" s="17"/>
-      <c r="AQ15" s="17"/>
-      <c r="AR15" s="17"/>
-      <c r="AS15" s="17"/>
-      <c r="AT15" s="17"/>
-      <c r="AU15" s="17"/>
-      <c r="AV15" s="17"/>
-      <c r="AW15" s="17"/>
-      <c r="AX15" s="17"/>
-      <c r="AY15" s="17"/>
-      <c r="AZ15" s="17"/>
-      <c r="BA15" s="17"/>
-      <c r="BB15" s="17"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
+      <c r="AC15" s="15"/>
+      <c r="AD15" s="15"/>
+      <c r="AE15" s="15"/>
+      <c r="AF15" s="15"/>
+      <c r="AG15" s="15"/>
+      <c r="AH15" s="15"/>
+      <c r="AI15" s="15"/>
+      <c r="AJ15" s="15"/>
+      <c r="AK15" s="15"/>
+      <c r="AL15" s="15"/>
+      <c r="AM15" s="15"/>
+      <c r="AN15" s="15"/>
+      <c r="AO15" s="15"/>
+      <c r="AP15" s="15"/>
+      <c r="AQ15" s="15"/>
+      <c r="AR15" s="15"/>
+      <c r="AS15" s="15"/>
+      <c r="AT15" s="15"/>
+      <c r="AU15" s="15"/>
+      <c r="AV15" s="15"/>
+      <c r="AW15" s="15"/>
+      <c r="AX15" s="15"/>
+      <c r="AY15" s="15"/>
+      <c r="AZ15" s="15"/>
+      <c r="BA15" s="15"/>
+      <c r="BB15" s="15"/>
     </row>
     <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="16">
         <f>SUM(B6:B15)</f>
         <v>200</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="16">
         <f>SUM(C6:C15)</f>
         <v>328.97999999999996</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="16">
         <f t="shared" ref="D16:H16" si="4">SUM(D6:D15)</f>
         <v>40</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="16">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="16">
         <f t="shared" si="4"/>
         <v>318.5</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="16">
         <f t="shared" si="4"/>
         <v>221.94</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="16">
         <f t="shared" si="4"/>
         <v>348.17</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="16">
         <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
         <v>229.10999999999999</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="16">
         <f t="shared" ref="J16" si="6">SUM(J6:J15)</f>
         <v>73.61</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="16">
         <f t="shared" ref="K16" si="7">SUM(K6:K15)</f>
         <v>50</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="16">
         <f t="shared" ref="L16" si="8">SUM(L6:L15)</f>
         <v>235.79</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="16">
         <f t="shared" ref="M16" si="9">SUM(M6:M15)</f>
         <v>54.36</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="16">
         <f t="shared" ref="N16" si="10">SUM(N6:N15)</f>
         <v>91.21</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="16">
         <f t="shared" ref="O16" si="11">SUM(O6:O15)</f>
         <v>388</v>
       </c>
-      <c r="P16" s="18">
+      <c r="P16" s="16">
         <f t="shared" ref="P16" si="12">SUM(P6:P15)</f>
         <v>90.5</v>
       </c>
-      <c r="Q16" s="18">
+      <c r="Q16" s="16">
         <f t="shared" ref="Q16" si="13">SUM(Q6:Q15)</f>
         <v>0</v>
       </c>
-      <c r="R16" s="18">
+      <c r="R16" s="16">
         <f t="shared" ref="R16" si="14">SUM(R6:R15)</f>
         <v>0</v>
       </c>
-      <c r="S16" s="18">
+      <c r="S16" s="16">
         <f t="shared" ref="S16" si="15">SUM(S6:S15)</f>
         <v>0</v>
       </c>
-      <c r="T16" s="18">
+      <c r="T16" s="16">
         <f t="shared" ref="T16" si="16">SUM(T6:T15)</f>
         <v>0</v>
       </c>
-      <c r="U16" s="18">
+      <c r="U16" s="16">
         <f t="shared" ref="U16" si="17">SUM(U6:U15)</f>
         <v>0</v>
       </c>
-      <c r="V16" s="18">
+      <c r="V16" s="16">
         <f t="shared" ref="V16" si="18">SUM(V6:V15)</f>
         <v>0</v>
       </c>
-      <c r="W16" s="18">
+      <c r="W16" s="16">
         <f t="shared" ref="W16" si="19">SUM(W6:W15)</f>
         <v>0</v>
       </c>
-      <c r="X16" s="18">
+      <c r="X16" s="16">
         <f t="shared" ref="X16" si="20">SUM(X6:X15)</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="18">
+      <c r="Y16" s="16">
         <f t="shared" ref="Y16" si="21">SUM(Y6:Y15)</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="18">
+      <c r="Z16" s="16">
         <f t="shared" ref="Z16" si="22">SUM(Z6:Z15)</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="18">
+      <c r="AA16" s="16">
         <f t="shared" ref="AA16" si="23">SUM(AA6:AA15)</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="18">
+      <c r="AB16" s="16">
         <f t="shared" ref="AB16" si="24">SUM(AB6:AB15)</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="18">
+      <c r="AC16" s="16">
         <f t="shared" ref="AC16" si="25">SUM(AC6:AC15)</f>
         <v>0</v>
       </c>
-      <c r="AD16" s="18">
+      <c r="AD16" s="16">
         <f t="shared" ref="AD16" si="26">SUM(AD6:AD15)</f>
         <v>0</v>
       </c>
-      <c r="AE16" s="18">
+      <c r="AE16" s="16">
         <f t="shared" ref="AE16" si="27">SUM(AE6:AE15)</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="18">
+      <c r="AF16" s="16">
         <f t="shared" ref="AF16" si="28">SUM(AF6:AF15)</f>
         <v>0</v>
       </c>
-      <c r="AG16" s="18">
+      <c r="AG16" s="16">
         <f t="shared" ref="AG16" si="29">SUM(AG6:AG15)</f>
         <v>0</v>
       </c>
-      <c r="AH16" s="18">
+      <c r="AH16" s="16">
         <f t="shared" ref="AH16" si="30">SUM(AH6:AH15)</f>
         <v>0</v>
       </c>
-      <c r="AI16" s="18">
+      <c r="AI16" s="16">
         <f t="shared" ref="AI16" si="31">SUM(AI6:AI15)</f>
         <v>0</v>
       </c>
-      <c r="AJ16" s="18">
+      <c r="AJ16" s="16">
         <f t="shared" ref="AJ16" si="32">SUM(AJ6:AJ15)</f>
         <v>0</v>
       </c>
-      <c r="AK16" s="18">
+      <c r="AK16" s="16">
         <f t="shared" ref="AK16" si="33">SUM(AK6:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AL16" s="18">
+      <c r="AL16" s="16">
         <f t="shared" ref="AL16" si="34">SUM(AL6:AL15)</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="18">
+      <c r="AM16" s="16">
         <f t="shared" ref="AM16" si="35">SUM(AM6:AM15)</f>
         <v>0</v>
       </c>
-      <c r="AN16" s="18">
+      <c r="AN16" s="16">
         <f t="shared" ref="AN16" si="36">SUM(AN6:AN15)</f>
         <v>0</v>
       </c>
-      <c r="AO16" s="18">
+      <c r="AO16" s="16">
         <f t="shared" ref="AO16" si="37">SUM(AO6:AO15)</f>
         <v>0</v>
       </c>
-      <c r="AP16" s="18">
+      <c r="AP16" s="16">
         <f t="shared" ref="AP16" si="38">SUM(AP6:AP15)</f>
         <v>0</v>
       </c>
-      <c r="AQ16" s="18">
+      <c r="AQ16" s="16">
         <f t="shared" ref="AQ16" si="39">SUM(AQ6:AQ15)</f>
         <v>0</v>
       </c>
-      <c r="AR16" s="18">
+      <c r="AR16" s="16">
         <f t="shared" ref="AR16" si="40">SUM(AR6:AR15)</f>
         <v>0</v>
       </c>
-      <c r="AS16" s="18">
+      <c r="AS16" s="16">
         <f t="shared" ref="AS16" si="41">SUM(AS6:AS15)</f>
         <v>0</v>
       </c>
-      <c r="AT16" s="18">
+      <c r="AT16" s="16">
         <f t="shared" ref="AT16" si="42">SUM(AT6:AT15)</f>
         <v>0</v>
       </c>
-      <c r="AU16" s="18">
+      <c r="AU16" s="16">
         <f t="shared" ref="AU16" si="43">SUM(AU6:AU15)</f>
         <v>0</v>
       </c>
-      <c r="AV16" s="18">
+      <c r="AV16" s="16">
         <f t="shared" ref="AV16" si="44">SUM(AV6:AV15)</f>
         <v>0</v>
       </c>
-      <c r="AW16" s="18">
+      <c r="AW16" s="16">
         <f t="shared" ref="AW16" si="45">SUM(AW6:AW15)</f>
         <v>0</v>
       </c>
-      <c r="AX16" s="18">
+      <c r="AX16" s="16">
         <f t="shared" ref="AX16" si="46">SUM(AX6:AX15)</f>
         <v>0</v>
       </c>
-      <c r="AY16" s="18">
+      <c r="AY16" s="16">
         <f t="shared" ref="AY16" si="47">SUM(AY6:AY15)</f>
         <v>0</v>
       </c>
-      <c r="AZ16" s="18">
+      <c r="AZ16" s="16">
         <f t="shared" ref="AZ16" si="48">SUM(AZ6:AZ15)</f>
         <v>0</v>
       </c>
-      <c r="BA16" s="18">
+      <c r="BA16" s="16">
         <f t="shared" ref="BA16" si="49">SUM(BA6:BA15)</f>
         <v>0</v>
       </c>
-      <c r="BB16" s="18">
+      <c r="BB16" s="16">
         <f t="shared" ref="BB16" si="50">SUM(BB6:BB15)</f>
         <v>0</v>
       </c>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{407F8550-187A-4887-B692-174281A0AF5A}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{397E3171-3E13-445A-B752-DA40560F7182}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
+    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -210,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -250,6 +250,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -592,8 +593,8 @@
     <col min="2" max="4" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="7"/>
@@ -618,15 +619,15 @@
       </c>
       <c r="B4" s="11">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C4" s="11">
         <f>SUM(Rounds!C6:BB6)</f>
-        <v>339.74</v>
+        <v>399.74</v>
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.2133571428571428</v>
+        <v>1.3324666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -635,7 +636,7 @@
       </c>
       <c r="B5" s="11">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C5" s="11">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -643,7 +644,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.1408214285714287</v>
+        <v>1.0647666666666666</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -652,7 +653,7 @@
       </c>
       <c r="B6" s="11">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C6" s="11">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -660,7 +661,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>0.79053571428571423</v>
+        <v>0.73783333333333334</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -669,7 +670,7 @@
       </c>
       <c r="B7" s="11">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C7" s="11">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -677,7 +678,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.0996071428571428</v>
+        <v>1.0263</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -686,7 +687,7 @@
       </c>
       <c r="B8" s="11">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C8" s="11">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -694,7 +695,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.71785714285714286</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -703,7 +704,7 @@
       </c>
       <c r="B9" s="11">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C9" s="11">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -711,7 +712,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.89910714285714288</v>
+        <v>0.83916666666666662</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -720,15 +721,15 @@
       </c>
       <c r="B10" s="11">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>292.68</v>
+        <v>311.88</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.0452857142857144</v>
+        <v>1.0396000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -737,15 +738,15 @@
       </c>
       <c r="B11" s="11">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C11" s="11">
         <f>SUM(Rounds!C13:BB13)</f>
-        <v>219.89</v>
+        <v>274.40999999999997</v>
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.7853214285714285</v>
+        <v>0.91469999999999985</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -754,7 +755,7 @@
       </c>
       <c r="B12" s="11">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -762,7 +763,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.46607142857142858</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -771,7 +772,7 @@
       </c>
       <c r="B13" s="11">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -779,7 +780,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.75335714285714284</v>
+        <v>0.70313333333333328</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -794,15 +795,15 @@
       </c>
       <c r="B15" s="13">
         <f>SUM(B4:B13)</f>
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="C15" s="12">
         <f>SUM(C4:C13)</f>
-        <v>2495.17</v>
+        <v>2628.89</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.89113214285714293</v>
+        <v>0.87629666666666661</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +826,7 @@
     <col min="3" max="54" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
@@ -835,15 +836,16 @@
         <v>19</v>
       </c>
       <c r="B2" s="18">
-        <v>690.33</v>
-      </c>
+        <v>624.04999999999995</v>
+      </c>
+      <c r="Q2" s="21"/>
     </row>
     <row r="3" spans="1:54" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1095,7 +1097,9 @@
         <v>68</v>
       </c>
       <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
+      <c r="Q6" s="15">
+        <v>60</v>
+      </c>
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
       <c r="T6" s="15"/>
@@ -1522,7 +1526,9 @@
       <c r="P12" s="15">
         <v>14.5</v>
       </c>
-      <c r="Q12" s="15"/>
+      <c r="Q12" s="15">
+        <v>19.2</v>
+      </c>
       <c r="R12" s="15"/>
       <c r="S12" s="15"/>
       <c r="T12" s="15"/>
@@ -1591,7 +1597,9 @@
         <v>120</v>
       </c>
       <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
+      <c r="Q13" s="15">
+        <v>54.52</v>
+      </c>
       <c r="R13" s="15"/>
       <c r="S13" s="15"/>
       <c r="T13" s="15"/>
@@ -1830,7 +1838,7 @@
       </c>
       <c r="Q16" s="16">
         <f t="shared" ref="Q16" si="13">SUM(Q6:Q15)</f>
-        <v>0</v>
+        <v>133.72</v>
       </c>
       <c r="R16" s="16">
         <f t="shared" ref="R16" si="14">SUM(R6:R15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{397E3171-3E13-445A-B752-DA40560F7182}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16040D4C-9EE1-4833-B619-912949936580}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -267,6 +267,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -619,7 +623,7 @@
       </c>
       <c r="B4" s="11">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C4" s="11">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -627,7 +631,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.3324666666666667</v>
+        <v>1.1757058823529412</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -636,15 +640,15 @@
       </c>
       <c r="B5" s="11">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C5" s="11">
         <f>SUM(Rounds!C7:BB7)</f>
-        <v>319.43</v>
+        <v>418.67</v>
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.0647666666666666</v>
+        <v>1.2313823529411765</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -653,15 +657,15 @@
       </c>
       <c r="B6" s="11">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C6" s="11">
         <f>SUM(Rounds!C8:BB8)</f>
-        <v>221.35</v>
+        <v>284.75</v>
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>0.73783333333333334</v>
+        <v>0.83750000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -670,15 +674,15 @@
       </c>
       <c r="B7" s="11">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C7" s="11">
         <f>SUM(Rounds!C9:BB9)</f>
-        <v>307.89</v>
+        <v>505.89</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.0263</v>
+        <v>1.4879117647058824</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -687,7 +691,7 @@
       </c>
       <c r="B8" s="11">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C8" s="11">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -695,7 +699,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.67</v>
+        <v>0.5911764705882353</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -704,15 +708,15 @@
       </c>
       <c r="B9" s="11">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C9" s="11">
         <f>SUM(Rounds!C11:BB11)</f>
-        <v>251.75</v>
+        <v>307.62</v>
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.83916666666666662</v>
+        <v>0.90476470588235292</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -721,15 +725,15 @@
       </c>
       <c r="B10" s="11">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>311.88</v>
+        <v>333.63</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>1.0396000000000001</v>
+        <v>0.98126470588235293</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -738,15 +742,15 @@
       </c>
       <c r="B11" s="11">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C11" s="11">
         <f>SUM(Rounds!C13:BB13)</f>
-        <v>274.40999999999997</v>
+        <v>348.40999999999997</v>
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.91469999999999985</v>
+        <v>1.0247352941176469</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -755,15 +759,15 @@
       </c>
       <c r="B12" s="11">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(Rounds!C14:BB14)</f>
-        <v>130.5</v>
+        <v>190.5</v>
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.435</v>
+        <v>0.56029411764705883</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -772,15 +776,15 @@
       </c>
       <c r="B13" s="11">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(Rounds!C15:BB15)</f>
-        <v>210.94</v>
+        <v>265.94</v>
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.70313333333333328</v>
+        <v>0.78217647058823525</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -795,15 +799,15 @@
       </c>
       <c r="B15" s="13">
         <f>SUM(B4:B13)</f>
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="C15" s="12">
         <f>SUM(C4:C13)</f>
-        <v>2628.89</v>
+        <v>3256.15</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.87629666666666661</v>
+        <v>0.95769117647058821</v>
       </c>
     </row>
   </sheetData>
@@ -818,7 +822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C68439-8736-4520-9CFB-113912EE56C5}">
-  <dimension ref="A1:BB16"/>
+  <dimension ref="A1:BB19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -836,7 +840,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="18">
-        <v>624.04999999999995</v>
+        <v>831.31</v>
       </c>
       <c r="Q2" s="21"/>
     </row>
@@ -845,7 +849,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1171,8 +1175,12 @@
         <v>41</v>
       </c>
       <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
+      <c r="R7" s="15">
+        <v>61.24</v>
+      </c>
+      <c r="S7" s="15">
+        <v>38</v>
+      </c>
       <c r="T7" s="15"/>
       <c r="U7" s="15"/>
       <c r="V7" s="15"/>
@@ -1240,7 +1248,10 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
+      <c r="R8" s="15">
+        <f>37.59+25.81</f>
+        <v>63.400000000000006</v>
+      </c>
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
       <c r="U8" s="15"/>
@@ -1307,8 +1318,12 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
+      <c r="R9" s="15">
+        <v>58</v>
+      </c>
+      <c r="S9" s="15">
+        <v>140</v>
+      </c>
       <c r="T9" s="15"/>
       <c r="U9" s="15"/>
       <c r="V9" s="15"/>
@@ -1449,7 +1464,9 @@
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
+      <c r="R11" s="15">
+        <v>55.87</v>
+      </c>
       <c r="S11" s="15"/>
       <c r="T11" s="15"/>
       <c r="U11" s="15"/>
@@ -1530,7 +1547,9 @@
         <v>19.2</v>
       </c>
       <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
+      <c r="S12" s="15">
+        <v>21.75</v>
+      </c>
       <c r="T12" s="15"/>
       <c r="U12" s="15"/>
       <c r="V12" s="15"/>
@@ -1601,7 +1620,9 @@
         <v>54.52</v>
       </c>
       <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
+      <c r="S13" s="15">
+        <v>74</v>
+      </c>
       <c r="T13" s="15"/>
       <c r="U13" s="15"/>
       <c r="V13" s="15"/>
@@ -1668,7 +1689,9 @@
       <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
       <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="15">
+        <v>60</v>
+      </c>
       <c r="T14" s="15"/>
       <c r="U14" s="15"/>
       <c r="V14" s="15"/>
@@ -1735,7 +1758,9 @@
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
+      <c r="S15" s="15">
+        <v>55</v>
+      </c>
       <c r="T15" s="15"/>
       <c r="U15" s="15"/>
       <c r="V15" s="15"/>
@@ -1842,11 +1867,11 @@
       </c>
       <c r="R16" s="16">
         <f t="shared" ref="R16" si="14">SUM(R6:R15)</f>
-        <v>0</v>
+        <v>238.51000000000002</v>
       </c>
       <c r="S16" s="16">
         <f t="shared" ref="S16" si="15">SUM(S6:S15)</f>
-        <v>0</v>
+        <v>388.75</v>
       </c>
       <c r="T16" s="16">
         <f t="shared" ref="T16" si="16">SUM(T6:T15)</f>
@@ -1988,6 +2013,9 @@
         <f t="shared" ref="BB16" si="50">SUM(BB6:BB15)</f>
         <v>0</v>
       </c>
+    </row>
+    <row r="19" spans="18:18" x14ac:dyDescent="0.2">
+      <c r="R19" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="347" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16040D4C-9EE1-4833-B619-912949936580}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE521AE4-5899-4016-9E22-14CB7D225EF0}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -267,10 +267,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,7 +619,7 @@
       </c>
       <c r="B4" s="11">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C4" s="11">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -631,7 +627,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.1757058823529412</v>
+        <v>1.1103888888888889</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -640,15 +636,15 @@
       </c>
       <c r="B5" s="11">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C5" s="11">
         <f>SUM(Rounds!C7:BB7)</f>
-        <v>418.67</v>
+        <v>441.88</v>
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.2313823529411765</v>
+        <v>1.2274444444444443</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -657,7 +653,7 @@
       </c>
       <c r="B6" s="11">
         <f>+Rounds!B8*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C6" s="11">
         <f>SUM(Rounds!C8:BB8)</f>
@@ -665,7 +661,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>0.83750000000000002</v>
+        <v>0.79097222222222219</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -674,7 +670,7 @@
       </c>
       <c r="B7" s="11">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C7" s="11">
         <f>SUM(Rounds!C9:BB9)</f>
@@ -682,7 +678,7 @@
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.4879117647058824</v>
+        <v>1.4052499999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -691,7 +687,7 @@
       </c>
       <c r="B8" s="11">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C8" s="11">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -699,7 +695,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.5911764705882353</v>
+        <v>0.55833333333333335</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -708,7 +704,7 @@
       </c>
       <c r="B9" s="11">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C9" s="11">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -716,7 +712,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.90476470588235292</v>
+        <v>0.85450000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -725,15 +721,15 @@
       </c>
       <c r="B10" s="11">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>333.63</v>
+        <v>356.63</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>0.98126470588235293</v>
+        <v>0.99063888888888885</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -742,7 +738,7 @@
       </c>
       <c r="B11" s="11">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C11" s="11">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -750,7 +746,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>1.0247352941176469</v>
+        <v>0.96780555555555547</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -759,7 +755,7 @@
       </c>
       <c r="B12" s="11">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -767,7 +763,7 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.56029411764705883</v>
+        <v>0.52916666666666667</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -776,7 +772,7 @@
       </c>
       <c r="B13" s="11">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -784,7 +780,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.78217647058823525</v>
+        <v>0.73872222222222217</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -799,15 +795,15 @@
       </c>
       <c r="B15" s="13">
         <f>SUM(B4:B13)</f>
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="C15" s="12">
         <f>SUM(C4:C13)</f>
-        <v>3256.15</v>
+        <v>3302.3599999999997</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.95769117647058821</v>
+        <v>0.91732222222222215</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +845,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1181,7 +1177,9 @@
       <c r="S7" s="15">
         <v>38</v>
       </c>
-      <c r="T7" s="15"/>
+      <c r="T7" s="15">
+        <v>23.21</v>
+      </c>
       <c r="U7" s="15"/>
       <c r="V7" s="15"/>
       <c r="W7" s="15"/>
@@ -1550,7 +1548,9 @@
       <c r="S12" s="15">
         <v>21.75</v>
       </c>
-      <c r="T12" s="15"/>
+      <c r="T12" s="15">
+        <v>23</v>
+      </c>
       <c r="U12" s="15"/>
       <c r="V12" s="15"/>
       <c r="W12" s="15"/>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="T16" s="16">
         <f t="shared" ref="T16" si="16">SUM(T6:T15)</f>
-        <v>0</v>
+        <v>46.21</v>
       </c>
       <c r="U16" s="16">
         <f t="shared" ref="U16" si="17">SUM(U6:U15)</f>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE521AE4-5899-4016-9E22-14CB7D225EF0}"/>
+  <xr:revisionPtr revIDLastSave="351" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302C2360-317B-4FDA-9D4D-C431CB9C97A6}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
+    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -267,6 +267,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -836,7 +840,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="18">
-        <v>831.31</v>
+        <v>702.54</v>
       </c>
       <c r="Q2" s="21"/>
     </row>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="351" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302C2360-317B-4FDA-9D4D-C431CB9C97A6}"/>
+  <xr:revisionPtr revIDLastSave="361" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB7F5948-F270-492A-9006-CF4D9102B640}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
+    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -267,10 +267,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,7 +619,7 @@
       </c>
       <c r="B4" s="11">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C4" s="11">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -631,7 +627,7 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.1103888888888889</v>
+        <v>1.0519473684210527</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -640,7 +636,7 @@
       </c>
       <c r="B5" s="11">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C5" s="11">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -648,7 +644,7 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.2274444444444443</v>
+        <v>1.1628421052631579</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -656,7 +652,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="11">
-        <f>+Rounds!B8*Rounds!$B$3</f>
+        <f>+Rounds!B8*Rounds!$B$3-20</f>
         <v>360</v>
       </c>
       <c r="C6" s="11">
@@ -665,7 +661,7 @@
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>0.79097222222222219</v>
+        <v>0.74934210526315792</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -674,15 +670,15 @@
       </c>
       <c r="B7" s="11">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C7" s="11">
         <f>SUM(Rounds!C9:BB9)</f>
-        <v>505.89</v>
+        <v>593.64</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.4052499999999999</v>
+        <v>1.5622105263157895</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -691,7 +687,7 @@
       </c>
       <c r="B8" s="11">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C8" s="11">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -699,7 +695,7 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.55833333333333335</v>
+        <v>0.52894736842105261</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -708,7 +704,7 @@
       </c>
       <c r="B9" s="11">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C9" s="11">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -716,7 +712,7 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.85450000000000004</v>
+        <v>0.80952631578947365</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -725,7 +721,7 @@
       </c>
       <c r="B10" s="11">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(Rounds!C12:BB12)</f>
@@ -733,7 +729,7 @@
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>0.99063888888888885</v>
+        <v>0.9385</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -742,7 +738,7 @@
       </c>
       <c r="B11" s="11">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C11" s="11">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -750,7 +746,7 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.96780555555555547</v>
+        <v>0.91686842105263144</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -759,15 +755,15 @@
       </c>
       <c r="B12" s="11">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(Rounds!C14:BB14)</f>
-        <v>190.5</v>
+        <v>260.5</v>
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.52916666666666667</v>
+        <v>0.68552631578947365</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -776,7 +772,7 @@
       </c>
       <c r="B13" s="11">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -784,7 +780,7 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.73872222222222217</v>
+        <v>0.69984210526315793</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -799,15 +795,15 @@
       </c>
       <c r="B15" s="13">
         <f>SUM(B4:B13)</f>
-        <v>3600</v>
+        <v>3780</v>
       </c>
       <c r="C15" s="12">
         <f>SUM(C4:C13)</f>
-        <v>3302.3599999999997</v>
+        <v>3460.1099999999997</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.91732222222222215</v>
+        <v>0.9105552631578947</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C68439-8736-4520-9CFB-113912EE56C5}">
-  <dimension ref="A1:BB19"/>
+  <dimension ref="A1:BB20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -840,7 +836,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="18">
-        <v>702.54</v>
+        <v>660.45</v>
       </c>
       <c r="Q2" s="21"/>
     </row>
@@ -849,7 +845,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="19">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1327,7 +1323,9 @@
         <v>140</v>
       </c>
       <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
+      <c r="U9" s="15">
+        <v>87.75</v>
+      </c>
       <c r="V9" s="15"/>
       <c r="W9" s="15"/>
       <c r="X9" s="15"/>
@@ -1697,7 +1695,9 @@
         <v>60</v>
       </c>
       <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
+      <c r="U14" s="15">
+        <v>70</v>
+      </c>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="U16" s="16">
         <f t="shared" ref="U16" si="17">SUM(U6:U15)</f>
-        <v>0</v>
+        <v>157.75</v>
       </c>
       <c r="V16" s="16">
         <f t="shared" ref="V16" si="18">SUM(V6:V15)</f>
@@ -2020,6 +2020,9 @@
     </row>
     <row r="19" spans="18:18" x14ac:dyDescent="0.2">
       <c r="R19" s="21"/>
+    </row>
+    <row r="20" spans="18:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="361" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB7F5948-F270-492A-9006-CF4D9102B640}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE5A02F1-3DE0-4B94-8EAE-9167A56C125E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
+    <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>Phil</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Sportsbet Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">]\[ </t>
   </si>
 </sst>
 </file>
@@ -210,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -251,6 +254,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -586,20 +590,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFEA29F7-65B3-44AC-A2EB-D5016B472E6E}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
     <col min="2" max="4" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="7"/>
     </row>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -613,13 +617,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="11">
         <f>+Rounds!B6*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C4" s="11">
         <f>SUM(Rounds!C6:BB6)</f>
@@ -627,16 +631,16 @@
       </c>
       <c r="D4" s="8">
         <f>+C4/(Rounds!$B$3*Rounds!B6)</f>
-        <v>1.0519473684210527</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.99935000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="11">
         <f>+Rounds!B7*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C5" s="11">
         <f>SUM(Rounds!C7:BB7)</f>
@@ -644,50 +648,50 @@
       </c>
       <c r="D5" s="8">
         <f>+C5/(Rounds!$B$3*Rounds!B7)</f>
-        <v>1.1628421052631579</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.1047</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="11">
         <f>+Rounds!B8*Rounds!$B$3-20</f>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C6" s="11">
         <f>SUM(Rounds!C8:BB8)</f>
-        <v>284.75</v>
+        <v>326.69</v>
       </c>
       <c r="D6" s="8">
         <f>+C6/(Rounds!$B$3*Rounds!B8)</f>
-        <v>0.74934210526315792</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.81672500000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="11">
         <f>+Rounds!B9*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Rounds!C9:BB9)</f>
-        <v>593.64</v>
+        <f>SUM(Rounds!C9:BB9)-431</f>
+        <v>200.64</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>1.5622105263157895</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.50159999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="11">
         <f>+Rounds!B10*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C8" s="11">
         <f>SUM(Rounds!C10:BB10)</f>
@@ -695,16 +699,17 @@
       </c>
       <c r="D8" s="8">
         <f>+C8/(Rounds!$B$3*Rounds!B10)</f>
-        <v>0.52894736842105261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.50249999999999995</v>
+      </c>
+      <c r="I8" s="22"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11">
         <f>+Rounds!B11*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C9" s="11">
         <f>SUM(Rounds!C11:BB11)</f>
@@ -712,33 +717,33 @@
       </c>
       <c r="D9" s="8">
         <f>+C9/(Rounds!$B$3*Rounds!B11)</f>
-        <v>0.80952631578947365</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.76905000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="11">
         <f>+Rounds!B12*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(Rounds!C12:BB12)</f>
-        <v>356.63</v>
+        <v>408.53</v>
       </c>
       <c r="D10" s="8">
         <f>+C10/(Rounds!$B$3*Rounds!B12)</f>
-        <v>0.9385</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1.021325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="11">
         <f>+Rounds!B13*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C11" s="11">
         <f>SUM(Rounds!C13:BB13)</f>
@@ -746,16 +751,16 @@
       </c>
       <c r="D11" s="8">
         <f>+C11/(Rounds!$B$3*Rounds!B13)</f>
-        <v>0.91686842105263144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.87102499999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="11">
         <f>+Rounds!B14*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(Rounds!C14:BB14)</f>
@@ -763,16 +768,16 @@
       </c>
       <c r="D12" s="8">
         <f>+C12/(Rounds!$B$3*Rounds!B14)</f>
-        <v>0.68552631578947365</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.65125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="11">
         <f>+Rounds!B15*Rounds!$B$3</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(Rounds!C15:BB15)</f>
@@ -780,30 +785,35 @@
       </c>
       <c r="D13" s="8">
         <f>+C13/(Rounds!$B$3*Rounds!B15)</f>
-        <v>0.69984210526315793</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.66484999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="13">
         <f>SUM(B4:B13)</f>
-        <v>3780</v>
+        <v>3980</v>
       </c>
       <c r="C15" s="12">
-        <f>SUM(C4:C13)</f>
-        <v>3460.1099999999997</v>
+        <f>SUM(C4:C13)+431</f>
+        <v>3591.9499999999994</v>
       </c>
       <c r="D15" s="10">
         <f>+C15/(Rounds!$B$3*Rounds!B16)</f>
-        <v>0.9105552631578947</v>
+        <v>0.89798749999999983</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +846,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="18">
-        <v>660.45</v>
+        <v>592.29</v>
       </c>
       <c r="Q2" s="21"/>
     </row>
@@ -845,7 +855,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.2">
@@ -1253,7 +1263,9 @@
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
       <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
+      <c r="V8" s="15">
+        <v>41.94</v>
+      </c>
       <c r="W8" s="15"/>
       <c r="X8" s="15"/>
       <c r="Y8" s="15"/>
@@ -1326,7 +1338,9 @@
       <c r="U9" s="15">
         <v>87.75</v>
       </c>
-      <c r="V9" s="15"/>
+      <c r="V9" s="15">
+        <v>38</v>
+      </c>
       <c r="W9" s="15"/>
       <c r="X9" s="15"/>
       <c r="Y9" s="15"/>
@@ -1554,7 +1568,9 @@
         <v>23</v>
       </c>
       <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
+      <c r="V12" s="15">
+        <v>51.9</v>
+      </c>
       <c r="W12" s="15"/>
       <c r="X12" s="15"/>
       <c r="Y12" s="15"/>
@@ -1887,7 +1903,7 @@
       </c>
       <c r="V16" s="16">
         <f t="shared" ref="V16" si="18">SUM(V6:V15)</f>
-        <v>0</v>
+        <v>131.84</v>
       </c>
       <c r="W16" s="16">
         <f t="shared" ref="W16" si="19">SUM(W6:W15)</f>
@@ -2018,11 +2034,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="18:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="18:22" x14ac:dyDescent="0.2">
       <c r="R19" s="21"/>
     </row>
-    <row r="20" spans="18:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="18:22" x14ac:dyDescent="0.2">
       <c r="R20" s="21"/>
+      <c r="V20" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Punters Club Puntoff.xlsx
+++ b/Punters Club Puntoff.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6011b6495b8904e4/Documents/Ian/Tips/Punters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maree\OneDrive\Documents\Ian\Tips\Punters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="8_{09DE6AF2-D661-4051-8769-A551AD4E0A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE5A02F1-3DE0-4B94-8EAE-9167A56C125E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFE139D-88C0-467C-B499-DB9783E7011A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C5D5C863-041B-4852-962B-338AE112943A}"/>
   </bookViews>
@@ -677,12 +677,12 @@
         <v>400</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Rounds!C9:BB9)-431</f>
-        <v>200.64</v>
+        <f>SUM(Rounds!C9:BB9)</f>
+        <v>631.64</v>
       </c>
       <c r="D7" s="8">
         <f>+C7/(Rounds!$B$3*Rounds!B9)</f>
-        <v>0.50159999999999993</v>
+        <v>1.5790999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -803,7 +803,7 @@
         <v>3980</v>
       </c>
       <c r="C15" s="12">
-        <f>SUM(C4:C13)+431</f>
+        <f>SUM(C4:C13)</f>
         <v>3591.9499999999994</v>
       </c>
       <c r="D15" s="10">
